--- a/results/feature_selection/global_ind/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/qP_calc/metrics_global.xlsx
@@ -488,46 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t_ind, t_ind_ad, I, X_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8773361950438064</v>
+        <v>0.7900934191719475</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001599017491697985</v>
+        <v>0.001941154405445864</v>
       </c>
       <c r="F2" t="n">
-        <v>5.847766841364449e-06</v>
+        <v>1.000690255441561e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002418215631693015</v>
+        <v>0.003163368861580263</v>
       </c>
       <c r="H2" t="n">
-        <v>321.4176868202302</v>
+        <v>840.7295279892165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03830323492364703</v>
+        <v>0.06547897908020384</v>
       </c>
       <c r="J2" t="n">
-        <v>-644.6703381304443</v>
+        <v>-611.6607141728508</v>
       </c>
       <c r="K2" t="n">
-        <v>-638.7033859907515</v>
+        <v>-601.7157939400295</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,350 +535,350 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8618619158191497</v>
+        <v>0.7815442013441743</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001687599874555805</v>
+        <v>0.001713297536518528</v>
       </c>
       <c r="F3" t="n">
-        <v>6.585474080890228e-06</v>
+        <v>1.041447048002095e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002566217855305786</v>
+        <v>0.003227145872132363</v>
       </c>
       <c r="H3" t="n">
-        <v>391.6025097199719</v>
+        <v>586.5892968345873</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04294603508611171</v>
+        <v>0.06704402972608373</v>
       </c>
       <c r="J3" t="n">
-        <v>-638.2547884901837</v>
+        <v>-613.5049736362141</v>
       </c>
       <c r="K3" t="n">
-        <v>-632.2878363504909</v>
+        <v>-607.5380214965213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dVdt_calc, Xlag1_calc</t>
+          <t>t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8492591134852965</v>
+        <v>0.3304769946740626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001674003255413335</v>
+        <v>0.002887412998584294</v>
       </c>
       <c r="F4" t="n">
-        <v>7.186289045194466e-06</v>
+        <v>3.19182535669256e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002680725469941759</v>
+        <v>0.005649624196964396</v>
       </c>
       <c r="H4" t="n">
-        <v>303.525678743072</v>
+        <v>1010.449631600268</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0497272963567427</v>
+        <v>0.2038792443752781</v>
       </c>
       <c r="J4" t="n">
-        <v>-621.5401249220087</v>
+        <v>-547.0259549835343</v>
       </c>
       <c r="K4" t="n">
-        <v>-603.6392685029302</v>
+        <v>-535.0920507041487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t, P, Plag1</t>
+          <t>t_ind, t_ind_ad</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7774133707070467</v>
+        <v>0.3081859193669741</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002226356762977964</v>
+        <v>0.004081765683313247</v>
       </c>
       <c r="F5" t="n">
-        <v>1.061140008313993e-05</v>
+        <v>3.298093877456041e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003257514402599002</v>
+        <v>0.005742903340172148</v>
       </c>
       <c r="H5" t="n">
-        <v>1034.017944669167</v>
+        <v>2841.561065151707</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06828341676794418</v>
+        <v>0.20856731084705</v>
       </c>
       <c r="J5" t="n">
-        <v>-612.4934093818018</v>
+        <v>-553.2573619187148</v>
       </c>
       <c r="K5" t="n">
-        <v>-606.526457242109</v>
+        <v>-549.2793938255862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7717905825272018</v>
+        <v>0.3015169227347929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002345451958688044</v>
+        <v>0.003113292117320884</v>
       </c>
       <c r="F6" t="n">
-        <v>1.087945596389348e-05</v>
+        <v>3.32988706810814e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003298402031877478</v>
+        <v>0.005770517366846875</v>
       </c>
       <c r="H6" t="n">
-        <v>980.1461257038447</v>
+        <v>1139.646472638142</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0689704408610142</v>
+        <v>0.2115682323890389</v>
       </c>
       <c r="J6" t="n">
-        <v>-615.1462533396862</v>
+        <v>-548.7393020518355</v>
       </c>
       <c r="K6" t="n">
-        <v>-613.1572692931219</v>
+        <v>-540.7833658655784</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t, t_ind_ad, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7625556468090904</v>
+        <v>0.230030970534235</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002578588423210561</v>
+        <v>0.002770489921939363</v>
       </c>
       <c r="F7" t="n">
-        <v>1.131971420383467e-05</v>
+        <v>3.670682937803423e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003364478295937525</v>
+        <v>0.006058616127304505</v>
       </c>
       <c r="H7" t="n">
-        <v>1154.101817673923</v>
+        <v>510.1208464738805</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07174122975721559</v>
+        <v>0.2325164036202942</v>
       </c>
       <c r="J7" t="n">
-        <v>-613.0040955560271</v>
+        <v>-545.4775776155218</v>
       </c>
       <c r="K7" t="n">
-        <v>-611.0151115094628</v>
+        <v>-539.510625475829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind_ad, P, I, mu_calc</t>
+          <t>t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7555245033451553</v>
+        <v>0.220184000651685</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002196167610596467</v>
+        <v>0.004784242797796921</v>
       </c>
       <c r="F8" t="n">
-        <v>1.165491078134146e-05</v>
+        <v>3.717626519887523e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003413928936187961</v>
+        <v>0.006097234225357857</v>
       </c>
       <c r="H8" t="n">
-        <v>917.0411359935681</v>
+        <v>2471.213834108078</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07535080743400036</v>
+        <v>0.2349708231901337</v>
       </c>
       <c r="J8" t="n">
-        <v>-605.4282787856182</v>
+        <v>-546.7913617605454</v>
       </c>
       <c r="K8" t="n">
-        <v>-597.4723425993611</v>
+        <v>-542.8133936674169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, T, mu_calc</t>
+          <t>t, t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7065704601632555</v>
+        <v>0.2183405706681455</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002780294801499262</v>
+        <v>0.002948222070293146</v>
       </c>
       <c r="F9" t="n">
-        <v>1.398870297515178e-05</v>
+        <v>3.726414726592809e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003740147453664331</v>
+        <v>0.006104436687027566</v>
       </c>
       <c r="H9" t="n">
-        <v>1458.657186252912</v>
+        <v>923.304971714856</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08953865404310596</v>
+        <v>0.2365239137026425</v>
       </c>
       <c r="J9" t="n">
-        <v>-597.5720661596982</v>
+        <v>-542.6638602148539</v>
       </c>
       <c r="K9" t="n">
-        <v>-591.6051140200054</v>
+        <v>-534.7079240285968</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.01475773030154726</v>
+        <v>0.1973362734297821</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006078596080583447</v>
+        <v>0.003006046163508141</v>
       </c>
       <c r="F10" t="n">
-        <v>4.696957735422304e-05</v>
+        <v>3.826548774253021e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006853435441749127</v>
+        <v>0.00618591042147639</v>
       </c>
       <c r="H10" t="n">
-        <v>3406.091387111132</v>
+        <v>865.017437420258</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2961055596136838</v>
+        <v>0.2418259038124852</v>
       </c>
       <c r="J10" t="n">
-        <v>-536.1645646333275</v>
+        <v>-545.2319572525506</v>
       </c>
       <c r="K10" t="n">
-        <v>-534.1755805867632</v>
+        <v>-541.2539891594221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>t_ind_ad, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.001639060137601955</v>
+        <v>0.1040757212348402</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006145695319539631</v>
+        <v>0.005380205932953409</v>
       </c>
       <c r="F11" t="n">
-        <v>4.759498534980017e-05</v>
+        <v>4.271150965525079e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006898911896074639</v>
+        <v>0.00653540432224746</v>
       </c>
       <c r="H11" t="n">
-        <v>3435.050891023838</v>
+        <v>2985.184510649456</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3000415984484643</v>
+        <v>0.2703071816863067</v>
       </c>
       <c r="J11" t="n">
-        <v>-535.4502902118174</v>
+        <v>-537.296274862837</v>
       </c>
       <c r="K11" t="n">
-        <v>-533.4613061652532</v>
+        <v>-531.3293227231442</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -886,32 +886,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4918482257422947</v>
+        <v>-0.1660279423775133</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007920216485257635</v>
+        <v>0.004700517945023036</v>
       </c>
       <c r="F12" t="n">
-        <v>7.112106615280471e-05</v>
+        <v>5.558819522983784e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008433330667820675</v>
+        <v>0.007455749139411669</v>
       </c>
       <c r="H12" t="n">
-        <v>4303.844482927447</v>
+        <v>1979.334579210557</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8962085049379909</v>
+        <v>0.7006945888998298</v>
       </c>
       <c r="J12" t="n">
-        <v>-513.7608567024358</v>
+        <v>-527.0671435440445</v>
       </c>
       <c r="K12" t="n">
-        <v>-511.7718726558716</v>
+        <v>-525.0781594974802</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wrapper/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wrapper/qP_calc/metrics_global.xlsx
@@ -488,391 +488,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I, X_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7900934191719475</v>
+        <v>0.7815442013441743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001941154405445864</v>
+        <v>0.001713297536518528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.000690255441561e-05</v>
+        <v>1.041447048002095e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003163368861580263</v>
+        <v>0.003227145872132363</v>
       </c>
       <c r="H2" t="n">
-        <v>840.7295279892165</v>
+        <v>586.5892968345873</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06547897908020384</v>
+        <v>0.06704402972608373</v>
       </c>
       <c r="J2" t="n">
-        <v>-611.6607141728508</v>
+        <v>-613.5049736362141</v>
       </c>
       <c r="K2" t="n">
-        <v>-601.7157939400295</v>
+        <v>-607.5380214965213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, I, X_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7815442013441743</v>
+        <v>0.6483717770071559</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001713297536518528</v>
+        <v>0.00235775916733154</v>
       </c>
       <c r="F3" t="n">
-        <v>1.041447048002095e-05</v>
+        <v>1.676321604111168e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003227145872132363</v>
+        <v>0.004094290663974857</v>
       </c>
       <c r="H3" t="n">
-        <v>586.5892968345873</v>
+        <v>817.7529739702455</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06704402972608373</v>
+        <v>0.108000201149082</v>
       </c>
       <c r="J3" t="n">
-        <v>-613.5049736362141</v>
+        <v>-583.8014740448946</v>
       </c>
       <c r="K3" t="n">
-        <v>-607.5380214965213</v>
+        <v>-573.8565538120732</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
+          <t>t, t_ind_ad</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3304769946740626</v>
+        <v>0.3315097121953369</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002887412998584294</v>
+        <v>0.004264877397334958</v>
       </c>
       <c r="F4" t="n">
-        <v>3.19182535669256e-05</v>
+        <v>3.186902069599386e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005649624196964396</v>
+        <v>0.005645265334419088</v>
       </c>
       <c r="H4" t="n">
-        <v>1010.449631600268</v>
+        <v>1749.161521007303</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2038792443752781</v>
+        <v>0.2015693946558862</v>
       </c>
       <c r="J4" t="n">
-        <v>-547.0259549835343</v>
+        <v>-555.1093125368694</v>
       </c>
       <c r="K4" t="n">
-        <v>-535.0920507041487</v>
+        <v>-551.1313444437409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad</t>
+          <t>t, t_ind_ad, mu_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.3081859193669741</v>
+        <v>0.3253262622330155</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004081765683313247</v>
+        <v>0.003896607076849472</v>
       </c>
       <c r="F5" t="n">
-        <v>3.298093877456041e-05</v>
+        <v>3.216380507568771e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005742903340172148</v>
+        <v>0.005671314228262061</v>
       </c>
       <c r="H5" t="n">
-        <v>2841.561065151707</v>
+        <v>1989.725878788993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.20856731084705</v>
+        <v>0.2039246359936484</v>
       </c>
       <c r="J5" t="n">
-        <v>-553.2573619187148</v>
+        <v>-552.6121153956057</v>
       </c>
       <c r="K5" t="n">
-        <v>-549.2793938255862</v>
+        <v>-546.6451632559128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t_ind_ad, T, I, V_calc</t>
+          <t>t, t_ind_ad, X_calc, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3015169227347929</v>
+        <v>0.3091080757750597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003113292117320884</v>
+        <v>0.003042046827443131</v>
       </c>
       <c r="F6" t="n">
-        <v>3.32988706810814e-05</v>
+        <v>3.293697669733902e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005770517366846875</v>
+        <v>0.005739074550599514</v>
       </c>
       <c r="H6" t="n">
-        <v>1139.646472638142</v>
+        <v>1101.749970150015</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2115682323890389</v>
+        <v>0.2102906331511703</v>
       </c>
       <c r="J6" t="n">
-        <v>-548.7393020518355</v>
+        <v>-545.3293894549292</v>
       </c>
       <c r="K6" t="n">
-        <v>-540.7833658655784</v>
+        <v>-533.3954851755436</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, mu_calc</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.230030970534235</v>
+        <v>0.3015169227347929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002770489921939363</v>
+        <v>0.003113292117320884</v>
       </c>
       <c r="F7" t="n">
-        <v>3.670682937803423e-05</v>
+        <v>3.32988706810814e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006058616127304505</v>
+        <v>0.005770517366846875</v>
       </c>
       <c r="H7" t="n">
-        <v>510.1208464738805</v>
+        <v>1139.646472638142</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2325164036202942</v>
+        <v>0.2115682323890389</v>
       </c>
       <c r="J7" t="n">
-        <v>-545.4775776155218</v>
+        <v>-548.7393020518355</v>
       </c>
       <c r="K7" t="n">
-        <v>-539.510625475829</v>
+        <v>-540.7833658655784</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, mu_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.220184000651685</v>
+        <v>0.230030970534235</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004784242797796921</v>
+        <v>0.002770489921939363</v>
       </c>
       <c r="F8" t="n">
-        <v>3.717626519887523e-05</v>
+        <v>3.670682937803423e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006097234225357857</v>
+        <v>0.006058616127304505</v>
       </c>
       <c r="H8" t="n">
-        <v>2471.213834108078</v>
+        <v>510.1208464738805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2349708231901337</v>
+        <v>0.2325164036202942</v>
       </c>
       <c r="J8" t="n">
-        <v>-546.7913617605454</v>
+        <v>-545.4775776155218</v>
       </c>
       <c r="K8" t="n">
-        <v>-542.8133936674169</v>
+        <v>-539.510625475829</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t, t_ind_ad, T, V_calc</t>
+          <t>t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2183405706681455</v>
+        <v>0.220184000651685</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002948222070293146</v>
+        <v>0.004784242797796921</v>
       </c>
       <c r="F9" t="n">
-        <v>3.726414726592809e-05</v>
+        <v>3.717626519887523e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006104436687027566</v>
+        <v>0.006097234225357857</v>
       </c>
       <c r="H9" t="n">
-        <v>923.304971714856</v>
+        <v>2471.213834108078</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2365239137026425</v>
+        <v>0.2349708231901337</v>
       </c>
       <c r="J9" t="n">
-        <v>-542.6638602148539</v>
+        <v>-546.7913617605454</v>
       </c>
       <c r="K9" t="n">
-        <v>-534.7079240285968</v>
+        <v>-542.8133936674169</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>t, t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1973362734297821</v>
+        <v>0.2183405706681455</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003006046163508141</v>
+        <v>0.002948222070293146</v>
       </c>
       <c r="F10" t="n">
-        <v>3.826548774253021e-05</v>
+        <v>3.726414726592809e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00618591042147639</v>
+        <v>0.006104436687027566</v>
       </c>
       <c r="H10" t="n">
-        <v>865.017437420258</v>
+        <v>923.304971714856</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2418259038124852</v>
+        <v>0.2365239137026425</v>
       </c>
       <c r="J10" t="n">
-        <v>-545.2319572525506</v>
+        <v>-542.6638602148539</v>
       </c>
       <c r="K10" t="n">
-        <v>-541.2539891594221</v>
+        <v>-534.7079240285968</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t_ind_ad, X_calc, V_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1040757212348402</v>
+        <v>0.1973362734297821</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005380205932953409</v>
+        <v>0.003006046163508141</v>
       </c>
       <c r="F11" t="n">
-        <v>4.271150965525079e-05</v>
+        <v>3.826548774253021e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00653540432224746</v>
+        <v>0.00618591042147639</v>
       </c>
       <c r="H11" t="n">
-        <v>2985.184510649456</v>
+        <v>865.017437420258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2703071816863067</v>
+        <v>0.2418259038124852</v>
       </c>
       <c r="J11" t="n">
-        <v>-537.296274862837</v>
+        <v>-545.2319572525506</v>
       </c>
       <c r="K11" t="n">
-        <v>-531.3293227231442</v>
+        <v>-541.2539891594221</v>
       </c>
     </row>
     <row r="12">
